--- a/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen dolor crónico</t>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,83</t>
+          <t>0,51; 6,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,17</t>
+          <t>0,69; 3,91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,41</t>
+          <t>0,93; 8,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,5</t>
+          <t>1,16; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,22</t>
+          <t>1,49; 7,19</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,75</t>
+          <t>0,61; 5,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,99</t>
+          <t>0,37; 4,89</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,24</t>
+          <t>2,19; 8,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,34</t>
+          <t>1,07; 6,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,39</t>
+          <t>2,25; 5,95</t>
         </is>
       </c>
     </row>
@@ -921,12 +922,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,06</t>
+          <t>1,27; 3,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,83</t>
+          <t>0,93; 2,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,49</t>
+          <t>1,28; 2,5</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 7008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6433</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2761</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>653; 7654</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1753; 9945</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2693</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4501</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>542; 4795</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>777; 6911</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1868; 9019</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1648</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3688</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2593</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>456; 4369</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4628</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2032</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>374; 5007</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5812</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4791</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10603</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2726; 10837</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1677; 10826</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6324; 16681</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 1713</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4327</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4669</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>13084</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>12743</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>8460; 20236</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7113; 21086</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>18255; 35664</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,83</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,03</t>
+          <t>0,58; 6,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,91</t>
+          <t>0,68; 4,09</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,23</t>
+          <t>0,91; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,29</t>
+          <t>1,0; 9,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,19</t>
+          <t>1,5; 6,83</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 9,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>0,0; 8,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,85</t>
+          <t>0,61; 6,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,89</t>
+          <t>0,35; 4,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,7</t>
+          <t>2,46; 8,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,94</t>
+          <t>1,1; 7,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,95</t>
+          <t>2,04; 6,45</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,04</t>
+          <t>1,28; 2,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,77</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,5</t>
+          <t>1,23; 2,51</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7008</t>
+          <t>0; 6890</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6433</t>
+          <t>0; 7875</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>653; 7654</t>
+          <t>741; 7634</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6792</t>
+          <t>0; 6870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1753; 9945</t>
+          <t>1728; 10398</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>542; 4795</t>
+          <t>532; 5071</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>777; 6911</t>
+          <t>673; 6075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1868; 9019</t>
+          <t>1886; 8571</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3688</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2593</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>456; 4369</t>
+          <t>454; 4479</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>0; 1810</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>374; 5007</t>
+          <t>359; 4654</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2726; 10837</t>
+          <t>3067; 10369</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1677; 10826</t>
+          <t>1711; 11054</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6324; 16681</t>
+          <t>5724; 18084</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1713</t>
+          <t>0; 1995</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4327</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4669</t>
+          <t>0; 4831</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8460; 20236</t>
+          <t>8534; 19397</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7113; 21086</t>
+          <t>7345; 20776</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18255; 35664</t>
+          <t>17531; 35836</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,68</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,02</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,38</t>
+          <t>0,8; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,09</t>
+          <t>0,85; 4,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,7</t>
+          <t>0,96; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,04</t>
+          <t>0,85; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,83</t>
+          <t>1,66; 7,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,22</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,0</t>
+          <t>0,66; 6,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,55</t>
+          <t>0,53; 5,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,33</t>
+          <t>0,98; 6,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,09</t>
+          <t>2,29; 8,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,45</t>
+          <t>2,16; 6,38</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,92</t>
+          <t>0,95; 2,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,34; 3,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,51</t>
+          <t>1,29; 2,54</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1106</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 4562</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 6890</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7875</t>
+          <t>0; 5914</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4761</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>741; 7634</t>
+          <t>0; 7087</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6870</t>
+          <t>809; 7503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1728; 10398</t>
+          <t>1844; 10129</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3965</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>532; 5071</t>
+          <t>570; 5351</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>673; 6075</t>
+          <t>481; 4705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1886; 8571</t>
+          <t>1919; 8773</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>630</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1729</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 2778</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>454; 4479</t>
+          <t>490; 4481</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>248</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1633</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4674</t>
+          <t>0; 1619</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1810</t>
+          <t>0; 4145</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359; 4654</t>
+          <t>505; 5131</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10012</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3067; 10369</t>
+          <t>1380; 9013</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1711; 11054</t>
+          <t>2805; 10480</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5724; 18084</t>
+          <t>5688; 16839</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>950</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1294</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1995</t>
+          <t>0; 5436</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5315</t>
+          <t>0; 1903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4831</t>
+          <t>0; 4982</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8534; 19397</t>
+          <t>6666; 19304</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7345; 20776</t>
+          <t>8451; 20185</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17531; 35836</t>
+          <t>17123; 33763</t>
         </is>
       </c>
     </row>
